--- a/results/demand/P3_isru_zbo_fixed_TEAM_LOW_DEMAND/results.xlsx
+++ b/results/demand/P3_isru_zbo_fixed_TEAM_LOW_DEMAND/results.xlsx
@@ -870,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1543,6 +1543,39 @@
       <c r="F21" t="inlineStr">
         <is>
           <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>undelivered_volume_paid</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>логическое</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>[true, false]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
         </is>
       </c>
     </row>
@@ -13665,18 +13698,18 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -13689,7 +13722,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -13714,18 +13747,18 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -13738,7 +13771,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -13763,18 +13796,18 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -13787,7 +13820,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -13812,18 +13845,18 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -13836,7 +13869,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -13861,18 +13894,18 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -13885,7 +13918,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -13910,18 +13943,18 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -13934,7 +13967,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -13959,7 +13992,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -13983,7 +14016,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2035-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14194,7 +14227,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -14218,7 +14251,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14429,11 +14462,11 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>116.8222443</v>
+        <v>92.44727349999999</v>
       </c>
       <c r="G45" t="n">
         <v>70</v>
@@ -14453,7 +14486,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2037-06, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14762,7 +14795,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -14786,7 +14819,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2038-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -15095,7 +15128,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -15119,7 +15152,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2039-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -15526,7 +15559,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -15550,7 +15583,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2040-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>

--- a/results/demand/P3_isru_zbo_fixed_TEAM_LOW_DEMAND/results.xlsx
+++ b/results/demand/P3_isru_zbo_fixed_TEAM_LOW_DEMAND/results.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -870,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1575,6 +1575,105 @@
       <c r="F22" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>exp10_demand_max</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>дополнительный относительный рост спроса</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>exp10_isru_reduction_max</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>exp10_price_half_range</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>относительное отклонение переменной цены от обязательного стресса</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>[-0.1, 0.1]</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
         </is>
       </c>

--- a/results/demand/P3_isru_zbo_fixed_TEAM_LOW_DEMAND/results.xlsx
+++ b/results/demand/P3_isru_zbo_fixed_TEAM_LOW_DEMAND/results.xlsx
@@ -7538,7 +7538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7647,6 +7647,11 @@
           <t>reservation_payment_mln</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7722,6 +7727,9 @@
       <c r="U2" t="n">
         <v>1.93647</v>
       </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7797,6 +7805,9 @@
       <c r="U3" t="n">
         <v>49.4442</v>
       </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7872,6 +7883,9 @@
       <c r="U4" t="n">
         <v>0</v>
       </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7947,6 +7961,9 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8022,6 +8039,9 @@
       <c r="U6" t="n">
         <v>0</v>
       </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8097,6 +8117,9 @@
       <c r="U7" t="n">
         <v>0</v>
       </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8172,6 +8195,9 @@
       <c r="U8" t="n">
         <v>68.8734</v>
       </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8247,6 +8273,9 @@
       <c r="U9" t="n">
         <v>0</v>
       </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8322,6 +8351,9 @@
       <c r="U10" t="n">
         <v>0</v>
       </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8397,6 +8429,9 @@
       <c r="U11" t="n">
         <v>0</v>
       </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8472,6 +8507,9 @@
       <c r="U12" t="n">
         <v>0</v>
       </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8547,6 +8585,9 @@
       <c r="U13" t="n">
         <v>85.5</v>
       </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8622,6 +8663,9 @@
       <c r="U14" t="n">
         <v>1.97835</v>
       </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8697,6 +8741,9 @@
       <c r="U15" t="n">
         <v>0</v>
       </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8772,6 +8819,9 @@
       <c r="U16" t="n">
         <v>0</v>
       </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8847,6 +8897,9 @@
       <c r="U17" t="n">
         <v>0</v>
       </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8922,6 +8975,9 @@
       <c r="U18" t="n">
         <v>72.7974</v>
       </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8997,6 +9053,9 @@
       <c r="U19" t="n">
         <v>0</v>
       </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9072,6 +9131,9 @@
       <c r="U20" t="n">
         <v>0</v>
       </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9147,6 +9209,9 @@
       <c r="U21" t="n">
         <v>0</v>
       </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9222,6 +9287,9 @@
       <c r="U22" t="n">
         <v>0</v>
       </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9297,6 +9365,9 @@
       <c r="U23" t="n">
         <v>85.5</v>
       </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9372,6 +9443,9 @@
       <c r="U24" t="n">
         <v>3.3933</v>
       </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9447,6 +9521,9 @@
       <c r="U25" t="n">
         <v>0</v>
       </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9522,6 +9599,9 @@
       <c r="U26" t="n">
         <v>0</v>
       </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9597,6 +9677,9 @@
       <c r="U27" t="n">
         <v>0</v>
       </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9672,6 +9755,9 @@
       <c r="U28" t="n">
         <v>85.5</v>
       </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9747,6 +9833,9 @@
       <c r="U29" t="n">
         <v>12.71055</v>
       </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9822,6 +9911,9 @@
       <c r="U30" t="n">
         <v>0</v>
       </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9897,6 +9989,9 @@
       <c r="U31" t="n">
         <v>0</v>
       </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9970,6 +10065,9 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9984,7 +10082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10048,6 +10146,11 @@
           <t>cumulative_capex_mln</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10090,6 +10193,9 @@
       <c r="L2" t="n">
         <v>0</v>
       </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10132,6 +10238,9 @@
       <c r="L3" t="n">
         <v>1250</v>
       </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10174,6 +10283,9 @@
       <c r="L4" t="n">
         <v>1430</v>
       </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10216,6 +10328,9 @@
       <c r="L5" t="n">
         <v>1430</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10258,6 +10373,9 @@
       <c r="L6" t="n">
         <v>1430</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10299,6 +10417,9 @@
       </c>
       <c r="L7" t="n">
         <v>1430</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -24685,7 +24806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25123,11 +25244,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>opening_inventory_t</t>
+          <t>take_or_pay_topup_mln</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.328859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -25143,11 +25264,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>closing_inventory_t</t>
+          <t>opening_inventory_t</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>326.0825855000001</v>
+        <v>12.328859</v>
       </c>
     </row>
     <row r="24">
@@ -25163,11 +25284,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>closing_inventory_t</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>40</v>
+        <v>326.0825855000001</v>
       </c>
     </row>
     <row r="25">
@@ -25183,11 +25304,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26">
@@ -25203,11 +25324,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>guideline_violations</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -25223,11 +25344,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D27" t="b">
-        <v>0</v>
+          <t>warnings</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="28">
@@ -25243,11 +25364,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>checks_total</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>75</v>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -25263,10 +25384,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D30" t="n">
         <v>70</v>
       </c>
     </row>

--- a/results/demand/P3_isru_zbo_fixed_TEAM_LOW_DEMAND/results.xlsx
+++ b/results/demand/P3_isru_zbo_fixed_TEAM_LOW_DEMAND/results.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="preparatory_period" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="contract_reserve_proof" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>40 / 0 / 9</t>
+          <t>89 / 0 / 0</t>
         </is>
       </c>
     </row>
@@ -578,7 +580,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions, preparatory_period, contract_reserve_proof</t>
         </is>
       </c>
     </row>
@@ -870,7 +872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1394,7 +1396,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>"end_of_month_hard_peak_warning"</t>
+          <t>"end_of_month_and_intra_month_peak_hard"</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1414,24 +1416,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
+          <t>Оба превышения ёмкости — жёсткие нарушения. Проверяется запас на конец месяца и расчётный пик внутри месяца при заявленном дроблении поставок (intra_month_delivery_batches): физическая исполнимость плана доказывается графиком поступлений, а не пометкой допущения.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>emergency_reserve_equivalence</t>
+          <t>intra_month_delivery_batches</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>"stock_covers_lead_time_and_reserved_capacity_covers_45d"</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>правило</t>
+          <t>партий в месяц</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1441,29 +1443,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>[1, 4]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
+          <t>Месячный объём канала приходит N равными партиями, равномерно распределёнными по месяцу, при равномерной выдаче потребителям (конвенция организатора). Пик запаса после партии j равен I_нач + (j·нетто − (j−1)·выдача)/N, максимум берётся по j = 1..N. При N = 1 это запас сразу после единственного поступления, до выдачи, — консервативный край без допущения о внутримесячной синхронизации поставок и выдачи. При N → ∞ пик стремится к max(запас на начало, запас на конец). Выбрано N = 1: организатор не задаёт размер отдельной партии, и ни один принятый план команды не нуждается в дроблении. Чувствительность к N = 2 и N = 4 показана в results/intra_month/intra_month_capacity.md.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>opening_stock_reservation_years</t>
+          <t>emergency_reserve_equivalence</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>"contracted_batch_schedule_and_waiting_cover"</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>лет</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1473,29 +1475,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[0.0, 1.0]</t>
+          <t>null</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
+          <t>Договорный аварийный резерв засчитывается только при одновременном выполнении пяти условий, каждое из которых печатается отдельной строкой в contract_reserve_proof: (1) канал доступен в этом году; (2) договорный срок исполнения партии не быстрее срока поставки канала по данным организатора; (3) нетто-объём гарантированной партии после потерь хранилища &gt;= R_y; (4) зарезервированная мощность канала за вычетом обычных заказов года &gt;= партия × число активаций; (5) физический запас на начало года покрывает спрос за время активации плюс срок исполнения. Сам по себе лимит мощности канала (80 т/год) эквивалентности не доказывает. Если блок inventory_policy.emergency_contract не задан, эквивалентность не доказана и действует физический резерв. Правило следует кейсу, §«Начальный запас и резерв».</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>prep_period_holding_charged</t>
+          <t>opening_stock_reservation_years</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>логическое</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1505,176 +1507,319 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[true, false]</t>
+          <t>[0.0, 1.0]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>intra_year_demand_profile</t>
+          <t>prep_period_holding_charged</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>"uniform"</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>перечисление</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CASE_INPUT</t>
+          <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>["uniform"]</t>
+          <t>[true, false]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+          <t>Хранение начального запаса начисляется с фактического месяца поставки, а не с 2035-01: ранняя поставка начального запаса не хранится бесплатно. Правило то же, что и в основном периоде (трапеция): в месяц поставки средний запас равен половине поступления, в каждый последующий месяц подготовительного периода — полному нетто-запасу. Расход относится на первый финансовый год (2035), как закупка и плата за резерв подготовительного периода. Значение false выключает начисление и оставлено только для сопоставления с прежней версией расчёта.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>intra_year_demand_profile</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>"uniform"</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>перечисление</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>["uniform"]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>undelivered_volume_paid</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>логическое</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>CASE_INPUT</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>[true, false]</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
 </t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>exp10_demand_max</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>дополнительный относительный рост спроса</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
 </t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>exp10_isru_reduction_max</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
 </t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>exp10_price_half_range</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>относительное отклонение переменной цены от обязательного стресса</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>[-0.1, 0.1]</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>scenario_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>plan_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>storage_mode</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>opening_t</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>arrived_t</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>closing_t</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>holding_cost_mln</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2034-12</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.36986577</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>(empty)</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U73"/>
+  <dimension ref="A1:W73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2411,6 +2556,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>peak_stock_t</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>delivery_batches</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>inflow_A_t</t>
         </is>
       </c>
@@ -2483,6 +2638,12 @@
         <v>0.8020604900000001</v>
       </c>
       <c r="U2" t="n">
+        <v>21.07315733333333</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2554,6 +2715,12 @@
         <v>0.9267183900000003</v>
       </c>
       <c r="U3" t="n">
+        <v>23.150789</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2625,6 +2792,12 @@
         <v>1.05137629</v>
       </c>
       <c r="U4" t="n">
+        <v>25.22842066666667</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2696,6 +2869,12 @@
         <v>1.17603419</v>
       </c>
       <c r="U5" t="n">
+        <v>27.30605233333334</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2767,6 +2946,12 @@
         <v>1.300692090000001</v>
       </c>
       <c r="U6" t="n">
+        <v>29.38368400000001</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2838,6 +3023,12 @@
         <v>1.425349990000001</v>
       </c>
       <c r="U7" t="n">
+        <v>31.46131566666668</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2909,6 +3100,12 @@
         <v>1.550007890000001</v>
       </c>
       <c r="U8" t="n">
+        <v>33.53894733333335</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2980,6 +3177,12 @@
         <v>1.674665790000001</v>
       </c>
       <c r="U9" t="n">
+        <v>35.61657900000002</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3051,6 +3254,12 @@
         <v>1.79932369</v>
       </c>
       <c r="U10" t="n">
+        <v>37.69421066666668</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3122,6 +3331,12 @@
         <v>1.92398159</v>
       </c>
       <c r="U11" t="n">
+        <v>39.77184233333334</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3193,6 +3408,12 @@
         <v>2.04863949</v>
       </c>
       <c r="U12" t="n">
+        <v>41.849474</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3264,6 +3485,12 @@
         <v>2.173297390000001</v>
       </c>
       <c r="U13" t="n">
+        <v>43.92710566666667</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3335,6 +3562,12 @@
         <v>2.3210375125</v>
       </c>
       <c r="U14" t="n">
+        <v>49.44081141666667</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3406,6 +3639,12 @@
         <v>2.491859857500001</v>
       </c>
       <c r="U15" t="n">
+        <v>52.2878505</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3477,6 +3716,12 @@
         <v>2.662682202500001</v>
       </c>
       <c r="U16" t="n">
+        <v>55.13488958333334</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3548,6 +3793,12 @@
         <v>2.833504547500001</v>
       </c>
       <c r="U17" t="n">
+        <v>57.98192866666668</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3619,6 +3870,12 @@
         <v>3.0043268925</v>
       </c>
       <c r="U18" t="n">
+        <v>60.82896775000001</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3690,6 +3947,12 @@
         <v>3.175149237500001</v>
       </c>
       <c r="U19" t="n">
+        <v>63.67600683333335</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3761,6 +4024,12 @@
         <v>3.3459715825</v>
       </c>
       <c r="U20" t="n">
+        <v>66.52304591666667</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3832,6 +4101,12 @@
         <v>3.5167939275</v>
       </c>
       <c r="U21" t="n">
+        <v>69.370085</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3903,6 +4178,12 @@
         <v>3.6876162725</v>
       </c>
       <c r="U22" t="n">
+        <v>72.21712408333333</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3974,6 +4255,12 @@
         <v>3.8584386175</v>
       </c>
       <c r="U23" t="n">
+        <v>75.06416316666666</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4045,6 +4332,12 @@
         <v>4.0292609625</v>
       </c>
       <c r="U24" t="n">
+        <v>77.91120225</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4116,6 +4409,12 @@
         <v>4.2000833075</v>
       </c>
       <c r="U25" t="n">
+        <v>80.75824133333334</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4187,6 +4486,12 @@
         <v>4.390606307500001</v>
       </c>
       <c r="U26" t="n">
+        <v>87.59530225000002</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4258,6 +4563,12 @@
         <v>4.600829962500001</v>
       </c>
       <c r="U27" t="n">
+        <v>91.09902983333335</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4329,6 +4640,12 @@
         <v>4.8110536175</v>
       </c>
       <c r="U28" t="n">
+        <v>94.60275741666668</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4400,6 +4717,12 @@
         <v>5.0212772725</v>
       </c>
       <c r="U29" t="n">
+        <v>98.10648500000001</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4471,6 +4794,12 @@
         <v>5.2315009275</v>
       </c>
       <c r="U30" t="n">
+        <v>101.6102125833333</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4542,6 +4871,12 @@
         <v>5.4417245825</v>
       </c>
       <c r="U31" t="n">
+        <v>105.1139401666667</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4613,6 +4948,12 @@
         <v>5.668711263999999</v>
       </c>
       <c r="U32" t="n">
+        <v>109.1764353</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4684,6 +5025,12 @@
         <v>5.912460971999999</v>
       </c>
       <c r="U33" t="n">
+        <v>113.2389304333333</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4755,6 +5102,12 @@
         <v>6.156210679999998</v>
       </c>
       <c r="U34" t="n">
+        <v>117.3014255666667</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4826,6 +5179,12 @@
         <v>6.399960387999998</v>
       </c>
       <c r="U35" t="n">
+        <v>121.3639207</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4897,6 +5256,12 @@
         <v>6.643710095999999</v>
       </c>
       <c r="U36" t="n">
+        <v>125.4264158333333</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4968,6 +5333,12 @@
         <v>6.887459803999999</v>
       </c>
       <c r="U37" t="n">
+        <v>129.4889109666667</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5039,6 +5410,12 @@
         <v>6.908910015999999</v>
       </c>
       <c r="U38" t="n">
+        <v>130.1414229</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5110,6 +5487,12 @@
         <v>6.708060731999999</v>
       </c>
       <c r="U39" t="n">
+        <v>126.7939348333333</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5181,6 +5564,12 @@
         <v>6.803611447999998</v>
       </c>
       <c r="U40" t="n">
+        <v>133.3264467666666</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5252,6 +5641,12 @@
         <v>7.195562163999997</v>
       </c>
       <c r="U41" t="n">
+        <v>139.8589587</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5323,6 +5718,12 @@
         <v>7.587512879999998</v>
       </c>
       <c r="U42" t="n">
+        <v>146.3914706333333</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5394,6 +5795,12 @@
         <v>7.979463595999998</v>
       </c>
       <c r="U43" t="n">
+        <v>152.9239825666666</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5465,6 +5872,12 @@
         <v>8.371414311999999</v>
       </c>
       <c r="U44" t="n">
+        <v>159.4564945</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5536,6 +5949,12 @@
         <v>8.763365028000001</v>
       </c>
       <c r="U45" t="n">
+        <v>165.9890064333333</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5607,6 +6026,12 @@
         <v>9.155315744000001</v>
       </c>
       <c r="U46" t="n">
+        <v>172.5215183666667</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5678,6 +6103,12 @@
         <v>9.547266460000003</v>
       </c>
       <c r="U47" t="n">
+        <v>179.0540303000001</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5749,6 +6180,12 @@
         <v>9.939217176000005</v>
       </c>
       <c r="U48" t="n">
+        <v>185.5865422333334</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5820,6 +6257,12 @@
         <v>10.33116789200001</v>
       </c>
       <c r="U49" t="n">
+        <v>192.1190541666668</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5891,6 +6334,12 @@
         <v>10.708718602</v>
       </c>
       <c r="U50" t="n">
+        <v>202.8382325666668</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1</v>
+      </c>
+      <c r="W50" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5962,6 +6411,12 @@
         <v>11.07186930600001</v>
       </c>
       <c r="U51" t="n">
+        <v>208.8907443000001</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6033,6 +6488,12 @@
         <v>11.43502001</v>
       </c>
       <c r="U52" t="n">
+        <v>214.9432560333334</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1</v>
+      </c>
+      <c r="W52" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6104,6 +6565,12 @@
         <v>11.798170714</v>
       </c>
       <c r="U53" t="n">
+        <v>220.9957677666667</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1</v>
+      </c>
+      <c r="W53" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6175,6 +6642,12 @@
         <v>12.161321418</v>
       </c>
       <c r="U54" t="n">
+        <v>227.0482795</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1</v>
+      </c>
+      <c r="W54" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6246,6 +6719,12 @@
         <v>12.524472122</v>
       </c>
       <c r="U55" t="n">
+        <v>233.1007912333334</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6317,6 +6796,12 @@
         <v>12.887622826</v>
       </c>
       <c r="U56" t="n">
+        <v>239.1533029666667</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
+      <c r="W56" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6388,6 +6873,12 @@
         <v>13.25077353</v>
       </c>
       <c r="U57" t="n">
+        <v>245.2058147</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1</v>
+      </c>
+      <c r="W57" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6459,6 +6950,12 @@
         <v>13.613924234</v>
       </c>
       <c r="U58" t="n">
+        <v>251.2583264333333</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1</v>
+      </c>
+      <c r="W58" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6530,6 +7027,12 @@
         <v>13.977074938</v>
       </c>
       <c r="U59" t="n">
+        <v>257.3108381666667</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1</v>
+      </c>
+      <c r="W59" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6601,6 +7104,12 @@
         <v>14.340225642</v>
       </c>
       <c r="U60" t="n">
+        <v>263.3633499</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1</v>
+      </c>
+      <c r="W60" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6672,6 +7181,12 @@
         <v>14.703376346</v>
       </c>
       <c r="U61" t="n">
+        <v>269.4158616333333</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1</v>
+      </c>
+      <c r="W61" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6743,6 +7258,12 @@
         <v>15.079951841</v>
       </c>
       <c r="U62" t="n">
+        <v>280.5825330666667</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1</v>
+      </c>
+      <c r="W62" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6814,6 +7335,12 @@
         <v>15.469952127</v>
       </c>
       <c r="U63" t="n">
+        <v>287.0825378333333</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1</v>
+      </c>
+      <c r="W63" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6885,6 +7412,12 @@
         <v>15.859952413</v>
       </c>
       <c r="U64" t="n">
+        <v>293.5825426</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
+      <c r="W64" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6956,6 +7489,12 @@
         <v>16.249952699</v>
       </c>
       <c r="U65" t="n">
+        <v>300.0825473666667</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1</v>
+      </c>
+      <c r="W65" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7027,6 +7566,12 @@
         <v>16.639952985</v>
       </c>
       <c r="U66" t="n">
+        <v>306.5825521333334</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1</v>
+      </c>
+      <c r="W66" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7098,6 +7643,12 @@
         <v>17.029953271</v>
       </c>
       <c r="U67" t="n">
+        <v>313.0825569</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1</v>
+      </c>
+      <c r="W67" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7169,6 +7720,12 @@
         <v>17.419953557</v>
       </c>
       <c r="U68" t="n">
+        <v>319.5825616666667</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1</v>
+      </c>
+      <c r="W68" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7240,6 +7797,12 @@
         <v>17.80995384300001</v>
       </c>
       <c r="U69" t="n">
+        <v>326.0825664333334</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1</v>
+      </c>
+      <c r="W69" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7311,6 +7874,12 @@
         <v>18.199954129</v>
       </c>
       <c r="U70" t="n">
+        <v>332.5825712000001</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1</v>
+      </c>
+      <c r="W70" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7382,6 +7951,12 @@
         <v>18.589954415</v>
       </c>
       <c r="U71" t="n">
+        <v>339.0825759666668</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1</v>
+      </c>
+      <c r="W71" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7453,6 +8028,12 @@
         <v>18.979954701</v>
       </c>
       <c r="U72" t="n">
+        <v>345.5825807333334</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1</v>
+      </c>
+      <c r="W72" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7524,6 +8105,12 @@
         <v>19.36995498700001</v>
       </c>
       <c r="U73" t="n">
+        <v>352.0825855000001</v>
+      </c>
+      <c r="V73" t="n">
+        <v>1</v>
+      </c>
+      <c r="W73" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -10173,7 +10760,7 @@
         <v>51.38067</v>
       </c>
       <c r="F2" t="n">
-        <v>17.85214728</v>
+        <v>18.22201305</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -10182,13 +10769,13 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>865.3612372800001</v>
+        <v>865.73110305</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>865.3612372800001</v>
+        <v>865.73110305</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -10433,7 +11020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10511,12 +11098,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>запас после поступления 72.217 т превышает ёмкость хранилища Base storage 70.0 т внутри 2036-09 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 72.217 т превышает ёмкость хранилища Base storage 70.0 т в 2036-09 (поставка одной партией в начале месяца; запас на начало 60.037 т, нетто-поступление 12.180 т, выдача 9.333 т)</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -10553,12 +11140,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>запас после поступления 75.064 т превышает ёмкость хранилища Base storage 70.0 т внутри 2036-10 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 75.064 т превышает ёмкость хранилища Base storage 70.0 т в 2036-10 (поставка одной партией в начале месяца; запас на начало 62.884 т, нетто-поступление 12.180 т, выдача 9.333 т)</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -10595,12 +11182,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>запас после поступления 77.911 т превышает ёмкость хранилища Base storage 70.0 т внутри 2036-11 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 77.911 т превышает ёмкость хранилища Base storage 70.0 т в 2036-11 (поставка одной партией в начале месяца; запас на начало 65.731 т, нетто-поступление 12.180 т, выдача 9.333 т)</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -10674,7 +11261,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -10684,23 +11271,23 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>запас на конец месяца 74.929 т превышает ёмкость хранилища Base storage 70.0 т в 2037-01</t>
+          <t>пик запаса внутри месяца 80.758 т превышает ёмкость хранилища Base storage 70.0 т в 2036-12 (поставка одной партией в начале месяца; запас на начало 68.578 т, нетто-поступление 12.180 т, выдача 9.333 т)</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>74.92863558333335</v>
+        <v>80.75824133333334</v>
       </c>
       <c r="J6" t="n">
         <v>70</v>
       </c>
       <c r="K6" t="n">
-        <v>4.928635583333346</v>
+        <v>10.75824133333334</v>
       </c>
     </row>
     <row r="7">
@@ -10726,23 +11313,23 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>запас на конец месяца 78.432 т превышает ёмкость хранилища Base storage 70.0 т в 2037-02</t>
+          <t>запас на конец месяца 74.929 т превышает ёмкость хранилища Base storage 70.0 т в 2037-01</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>2037</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>78.43236316666668</v>
+        <v>74.92863558333335</v>
       </c>
       <c r="J7" t="n">
         <v>70</v>
       </c>
       <c r="K7" t="n">
-        <v>8.432363166666676</v>
+        <v>4.928635583333346</v>
       </c>
     </row>
     <row r="8">
@@ -10758,7 +11345,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -10768,23 +11355,23 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>запас на конец месяца 81.936 т превышает ёмкость хранилища Base storage 70.0 т в 2037-03</t>
+          <t>пик запаса внутри месяца 87.595 т превышает ёмкость хранилища Base storage 70.0 т в 2037-01 (поставка одной партией в начале месяца; запас на начало 71.425 т, нетто-поступление 16.170 т, выдача 12.667 т)</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>2037</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>81.93609075000001</v>
+        <v>87.59530225000002</v>
       </c>
       <c r="J8" t="n">
         <v>70</v>
       </c>
       <c r="K8" t="n">
-        <v>11.93609075000001</v>
+        <v>17.59530225000002</v>
       </c>
     </row>
     <row r="9">
@@ -10810,23 +11397,23 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>запас на конец месяца 85.440 т превышает ёмкость хранилища Base storage 70.0 т в 2037-04</t>
+          <t>запас на конец месяца 78.432 т превышает ёмкость хранилища Base storage 70.0 т в 2037-02</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>2037</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>85.43981833333333</v>
+        <v>78.43236316666668</v>
       </c>
       <c r="J9" t="n">
         <v>70</v>
       </c>
       <c r="K9" t="n">
-        <v>15.43981833333333</v>
+        <v>8.432363166666676</v>
       </c>
     </row>
     <row r="10">
@@ -10842,7 +11429,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -10852,23 +11439,23 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>запас на конец месяца 88.944 т превышает ёмкость хранилища Base storage 70.0 т в 2037-05</t>
+          <t>пик запаса внутри месяца 91.099 т превышает ёмкость хранилища Base storage 70.0 т в 2037-02 (поставка одной партией в начале месяца; запас на начало 74.929 т, нетто-поступление 16.170 т, выдача 12.667 т)</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>2037</v>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>88.94354591666666</v>
+        <v>91.09902983333335</v>
       </c>
       <c r="J10" t="n">
         <v>70</v>
       </c>
       <c r="K10" t="n">
-        <v>18.94354591666666</v>
+        <v>21.09902983333335</v>
       </c>
     </row>
     <row r="11">
@@ -10894,23 +11481,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>запас на конец месяца 92.447 т превышает ёмкость хранилища Base storage 70.0 т в 2037-06</t>
+          <t>запас на конец месяца 81.936 т превышает ёмкость хранилища Base storage 70.0 т в 2037-03</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>2037</v>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>92.44727349999999</v>
+        <v>81.93609075000001</v>
       </c>
       <c r="J11" t="n">
         <v>70</v>
       </c>
       <c r="K11" t="n">
-        <v>22.44727349999999</v>
+        <v>11.93609075000001</v>
       </c>
     </row>
     <row r="12">
@@ -10931,28 +11518,28 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>запас после поступления 121.364 т превышает ёмкость хранилища ZBO modernization 120.0 т внутри 2037-10 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 94.603 т превышает ёмкость хранилища Base storage 70.0 т в 2037-03 (поставка одной партией в начале месяца; запас на начало 78.432 т, нетто-поступление 16.170 т, выдача 12.667 т)</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>2037</v>
       </c>
       <c r="G12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>121.3639207</v>
+        <v>94.60275741666668</v>
       </c>
       <c r="J12" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="K12" t="n">
-        <v>1.36392069999998</v>
+        <v>24.60275741666668</v>
       </c>
     </row>
     <row r="13">
@@ -10968,33 +11555,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>INTRA_MONTH_PEAK</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>запас после поступления 125.426 т превышает ёмкость хранилища ZBO modernization 120.0 т внутри 2037-11 (до выдачи потребителям)</t>
+          <t>запас на конец месяца 85.440 т превышает ёмкость хранилища Base storage 70.0 т в 2037-04</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>2037</v>
       </c>
       <c r="G13" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>125.4264158333333</v>
+        <v>85.43981833333333</v>
       </c>
       <c r="J13" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="K13" t="n">
-        <v>5.426415833333309</v>
+        <v>15.43981833333333</v>
       </c>
     </row>
     <row r="14">
@@ -11015,28 +11602,28 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>запас после поступления 129.489 т превышает ёмкость хранилища ZBO modernization 120.0 т внутри 2037-12 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 98.106 т превышает ёмкость хранилища Base storage 70.0 т в 2037-04 (поставка одной партией в начале месяца; запас на начало 81.936 т, нетто-поступление 16.170 т, выдача 12.667 т)</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>2037</v>
       </c>
       <c r="G14" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>129.4889109666667</v>
+        <v>98.10648500000001</v>
       </c>
       <c r="J14" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="K14" t="n">
-        <v>9.488910966666651</v>
+        <v>28.10648500000001</v>
       </c>
     </row>
     <row r="15">
@@ -11052,33 +11639,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>INTRA_MONTH_PEAK</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>запас после поступления 130.141 т превышает ёмкость хранилища ZBO modernization 120.0 т внутри 2038-01 (до выдачи потребителям)</t>
+          <t>запас на конец месяца 88.944 т превышает ёмкость хранилища Base storage 70.0 т в 2037-05</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>130.1414229</v>
+        <v>88.94354591666666</v>
       </c>
       <c r="J15" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="K15" t="n">
-        <v>10.14142289999998</v>
+        <v>18.94354591666666</v>
       </c>
     </row>
     <row r="16">
@@ -11099,28 +11686,28 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>запас после поступления 126.794 т превышает ёмкость хранилища ZBO modernization 120.0 т внутри 2038-02 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 101.610 т превышает ёмкость хранилища Base storage 70.0 т в 2037-05 (поставка одной партией в начале месяца; запас на начало 85.440 т, нетто-поступление 16.170 т, выдача 12.667 т)</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>126.7939348333333</v>
+        <v>101.6102125833333</v>
       </c>
       <c r="J16" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="K16" t="n">
-        <v>6.793934833333296</v>
+        <v>31.61021258333334</v>
       </c>
     </row>
     <row r="17">
@@ -11136,33 +11723,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>INTRA_MONTH_PEAK</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>запас после поступления 133.326 т превышает ёмкость хранилища ZBO modernization 120.0 т внутри 2038-03 (до выдачи потребителям)</t>
+          <t>запас на конец месяца 92.447 т превышает ёмкость хранилища Base storage 70.0 т в 2037-06</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>133.3264467666666</v>
+        <v>92.44727349999999</v>
       </c>
       <c r="J17" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="K17" t="n">
-        <v>13.32644676666663</v>
+        <v>22.44727349999999</v>
       </c>
     </row>
     <row r="18">
@@ -11178,7 +11765,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -11188,23 +11775,23 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>запас на конец месяца 123.192 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-04</t>
+          <t>пик запаса внутри месяца 105.114 т превышает ёмкость хранилища Base storage 70.0 т в 2037-06 (поставка одной партией в начале месяца; запас на начало 88.944 т, нетто-поступление 16.170 т, выдача 12.667 т)</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="G18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>123.1922920333333</v>
+        <v>105.1139401666667</v>
       </c>
       <c r="J18" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="K18" t="n">
-        <v>3.192292033333288</v>
+        <v>35.11394016666667</v>
       </c>
     </row>
     <row r="19">
@@ -11220,7 +11807,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -11230,23 +11817,23 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>запас на конец месяца 129.725 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-05</t>
+          <t>пик запаса внутри месяца 121.364 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2037-10 (поставка одной партией в начале месяца; запас на начало 104.635 т, нетто-поступление 16.729 т, выдача 12.667 т)</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="G19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I19" t="n">
-        <v>129.7248039666666</v>
+        <v>121.3639207</v>
       </c>
       <c r="J19" t="n">
         <v>120</v>
       </c>
       <c r="K19" t="n">
-        <v>9.724803966666627</v>
+        <v>1.36392069999998</v>
       </c>
     </row>
     <row r="20">
@@ -11262,7 +11849,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -11272,23 +11859,23 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>запас на конец месяца 136.257 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-06</t>
+          <t>пик запаса внутри месяца 125.426 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2037-11 (поставка одной партией в начале месяца; запас на начало 108.697 т, нетто-поступление 16.729 т, выдача 12.667 т)</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="G20" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I20" t="n">
-        <v>136.2573159</v>
+        <v>125.4264158333333</v>
       </c>
       <c r="J20" t="n">
         <v>120</v>
       </c>
       <c r="K20" t="n">
-        <v>16.25731589999998</v>
+        <v>5.426415833333309</v>
       </c>
     </row>
     <row r="21">
@@ -11304,7 +11891,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -11314,23 +11901,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>запас на конец месяца 142.790 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-07</t>
+          <t>пик запаса внутри месяца 129.489 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2037-12 (поставка одной партией в начале месяца; запас на начало 112.760 т, нетто-поступление 16.729 т, выдача 12.667 т)</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="G21" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I21" t="n">
-        <v>142.7898278333333</v>
+        <v>129.4889109666667</v>
       </c>
       <c r="J21" t="n">
         <v>120</v>
       </c>
       <c r="K21" t="n">
-        <v>22.78982783333333</v>
+        <v>9.488910966666651</v>
       </c>
     </row>
     <row r="22">
@@ -11346,7 +11933,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -11356,23 +11943,23 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>запас на конец месяца 149.322 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-08</t>
+          <t>пик запаса внутри месяца 130.141 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-01 (поставка одной партией в начале месяца; запас на начало 116.822 т, нетто-поступление 13.319 т, выдача 16.667 т)</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>2038</v>
       </c>
       <c r="G22" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>149.3223397666667</v>
+        <v>130.1414229</v>
       </c>
       <c r="J22" t="n">
         <v>120</v>
       </c>
       <c r="K22" t="n">
-        <v>29.32233976666669</v>
+        <v>10.14142289999998</v>
       </c>
     </row>
     <row r="23">
@@ -11388,7 +11975,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -11398,23 +11985,23 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>запас на конец месяца 155.855 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-09</t>
+          <t>пик запаса внутри месяца 126.794 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-02 (поставка одной партией в начале месяца; запас на начало 113.475 т, нетто-поступление 13.319 т, выдача 16.667 т)</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>2038</v>
       </c>
       <c r="G23" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>155.8548517</v>
+        <v>126.7939348333333</v>
       </c>
       <c r="J23" t="n">
         <v>120</v>
       </c>
       <c r="K23" t="n">
-        <v>35.85485170000004</v>
+        <v>6.79393483333331</v>
       </c>
     </row>
     <row r="24">
@@ -11430,7 +12017,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -11440,23 +12027,23 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>запас на конец месяца 162.387 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-10</t>
+          <t>пик запаса внутри месяца 133.326 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-03 (поставка одной партией в начале месяца; запас на начало 110.127 т, нетто-поступление 23.199 т, выдача 16.667 т)</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>2038</v>
       </c>
       <c r="G24" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>162.3873636333334</v>
+        <v>133.3264467666666</v>
       </c>
       <c r="J24" t="n">
         <v>120</v>
       </c>
       <c r="K24" t="n">
-        <v>42.38736363333339</v>
+        <v>13.32644676666663</v>
       </c>
     </row>
     <row r="25">
@@ -11482,23 +12069,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>запас на конец месяца 168.920 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-11</t>
+          <t>запас на конец месяца 123.192 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-04</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>2038</v>
       </c>
       <c r="G25" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>168.9198755666667</v>
+        <v>123.1922920333333</v>
       </c>
       <c r="J25" t="n">
         <v>120</v>
       </c>
       <c r="K25" t="n">
-        <v>48.91987556666675</v>
+        <v>3.192292033333288</v>
       </c>
     </row>
     <row r="26">
@@ -11514,7 +12101,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -11524,23 +12111,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>запас на конец месяца 175.452 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-12</t>
+          <t>пик запаса внутри месяца 139.859 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-04 (поставка одной партией в начале месяца; запас на начало 116.660 т, нетто-поступление 23.199 т, выдача 16.667 т)</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>2038</v>
       </c>
       <c r="G26" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>175.4523875000001</v>
+        <v>139.8589587</v>
       </c>
       <c r="J26" t="n">
         <v>120</v>
       </c>
       <c r="K26" t="n">
-        <v>55.4523875000001</v>
+        <v>19.85895869999996</v>
       </c>
     </row>
     <row r="27">
@@ -11566,23 +12153,23 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>запас на конец месяца 181.505 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-01</t>
+          <t>запас на конец месяца 129.725 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-05</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I27" t="n">
-        <v>181.5048992333334</v>
+        <v>129.7248039666666</v>
       </c>
       <c r="J27" t="n">
         <v>120</v>
       </c>
       <c r="K27" t="n">
-        <v>61.50489923333342</v>
+        <v>9.724803966666627</v>
       </c>
     </row>
     <row r="28">
@@ -11598,7 +12185,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -11608,23 +12195,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>запас на конец месяца 187.557 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-02</t>
+          <t>пик запаса внутри месяца 146.391 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-05 (поставка одной партией в начале месяца; запас на начало 123.192 т, нетто-поступление 23.199 т, выдача 16.667 т)</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I28" t="n">
-        <v>187.5574109666667</v>
+        <v>146.3914706333333</v>
       </c>
       <c r="J28" t="n">
         <v>120</v>
       </c>
       <c r="K28" t="n">
-        <v>67.55741096666674</v>
+        <v>26.39147063333328</v>
       </c>
     </row>
     <row r="29">
@@ -11650,23 +12237,23 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>запас на конец месяца 193.610 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-03</t>
+          <t>запас на конец месяца 136.257 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-06</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>193.6099227000001</v>
+        <v>136.2573159</v>
       </c>
       <c r="J29" t="n">
         <v>120</v>
       </c>
       <c r="K29" t="n">
-        <v>73.60992270000006</v>
+        <v>16.25731589999998</v>
       </c>
     </row>
     <row r="30">
@@ -11682,7 +12269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -11692,23 +12279,23 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>запас на конец месяца 199.662 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-04</t>
+          <t>пик запаса внутри месяца 152.924 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-06 (поставка одной партией в начале месяца; запас на начало 129.725 т, нетто-поступление 23.199 т, выдача 16.667 т)</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="G30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I30" t="n">
-        <v>199.6624344333334</v>
+        <v>152.9239825666666</v>
       </c>
       <c r="J30" t="n">
         <v>120</v>
       </c>
       <c r="K30" t="n">
-        <v>79.66243443333337</v>
+        <v>32.92398256666664</v>
       </c>
     </row>
     <row r="31">
@@ -11734,23 +12321,23 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>запас на конец месяца 205.715 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-05</t>
+          <t>запас на конец месяца 142.790 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-07</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="G31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I31" t="n">
-        <v>205.7149461666667</v>
+        <v>142.7898278333333</v>
       </c>
       <c r="J31" t="n">
         <v>120</v>
       </c>
       <c r="K31" t="n">
-        <v>85.71494616666669</v>
+        <v>22.78982783333333</v>
       </c>
     </row>
     <row r="32">
@@ -11766,7 +12353,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -11776,23 +12363,23 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>запас на конец месяца 211.767 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-06</t>
+          <t>пик запаса внутри месяца 159.456 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-07 (поставка одной партией в начале месяца; запас на начало 136.257 т, нетто-поступление 23.199 т, выдача 16.667 т)</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="G32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I32" t="n">
-        <v>211.7674579</v>
+        <v>159.4564945</v>
       </c>
       <c r="J32" t="n">
         <v>120</v>
       </c>
       <c r="K32" t="n">
-        <v>91.76745790000001</v>
+        <v>39.45649449999999</v>
       </c>
     </row>
     <row r="33">
@@ -11818,23 +12405,23 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>запас на конец месяца 217.820 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-07</t>
+          <t>запас на конец месяца 149.322 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-08</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="G33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I33" t="n">
-        <v>217.8199696333333</v>
+        <v>149.3223397666667</v>
       </c>
       <c r="J33" t="n">
         <v>120</v>
       </c>
       <c r="K33" t="n">
-        <v>97.81996963333333</v>
+        <v>29.32233976666669</v>
       </c>
     </row>
     <row r="34">
@@ -11850,7 +12437,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -11860,23 +12447,23 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>запас на конец месяца 223.872 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-08</t>
+          <t>пик запаса внутри месяца 165.989 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-08 (поставка одной партией в начале месяца; запас на начало 142.790 т, нетто-поступление 23.199 т, выдача 16.667 т)</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="G34" t="n">
         <v>8</v>
       </c>
       <c r="I34" t="n">
-        <v>223.8724813666666</v>
+        <v>165.9890064333333</v>
       </c>
       <c r="J34" t="n">
         <v>120</v>
       </c>
       <c r="K34" t="n">
-        <v>103.8724813666666</v>
+        <v>45.98900643333334</v>
       </c>
     </row>
     <row r="35">
@@ -11902,23 +12489,23 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>запас на конец месяца 229.925 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-09</t>
+          <t>запас на конец месяца 155.855 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-09</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="G35" t="n">
         <v>9</v>
       </c>
       <c r="I35" t="n">
-        <v>229.9249931</v>
+        <v>155.8548517</v>
       </c>
       <c r="J35" t="n">
         <v>120</v>
       </c>
       <c r="K35" t="n">
-        <v>109.9249931</v>
+        <v>35.85485170000004</v>
       </c>
     </row>
     <row r="36">
@@ -11934,7 +12521,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -11944,23 +12531,23 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>запас на конец месяца 235.978 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-10</t>
+          <t>пик запаса внутри месяца 172.522 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-09 (поставка одной партией в начале месяца; запас на начало 149.322 т, нетто-поступление 23.199 т, выдача 16.667 т)</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="G36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I36" t="n">
-        <v>235.9775048333333</v>
+        <v>172.5215183666667</v>
       </c>
       <c r="J36" t="n">
         <v>120</v>
       </c>
       <c r="K36" t="n">
-        <v>115.9775048333333</v>
+        <v>52.5215183666667</v>
       </c>
     </row>
     <row r="37">
@@ -11986,23 +12573,23 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>запас на конец месяца 242.030 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-11</t>
+          <t>запас на конец месяца 162.387 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-10</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="G37" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I37" t="n">
-        <v>242.0300165666667</v>
+        <v>162.3873636333334</v>
       </c>
       <c r="J37" t="n">
         <v>120</v>
       </c>
       <c r="K37" t="n">
-        <v>122.0300165666667</v>
+        <v>42.38736363333339</v>
       </c>
     </row>
     <row r="38">
@@ -12018,7 +12605,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -12028,23 +12615,23 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>запас на конец месяца 248.083 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-12</t>
+          <t>пик запаса внутри месяца 179.054 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-10 (поставка одной партией в начале месяца; запас на начало 155.855 т, нетто-поступление 23.199 т, выдача 16.667 т)</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="G38" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I38" t="n">
-        <v>248.0825283</v>
+        <v>179.0540303000001</v>
       </c>
       <c r="J38" t="n">
         <v>120</v>
       </c>
       <c r="K38" t="n">
-        <v>128.0825283</v>
+        <v>59.05403030000005</v>
       </c>
     </row>
     <row r="39">
@@ -12070,23 +12657,23 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>запас на конец месяца 254.583 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-01</t>
+          <t>запас на конец месяца 168.920 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-11</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I39" t="n">
-        <v>254.5825330666667</v>
+        <v>168.9198755666667</v>
       </c>
       <c r="J39" t="n">
         <v>120</v>
       </c>
       <c r="K39" t="n">
-        <v>134.5825330666667</v>
+        <v>48.91987556666675</v>
       </c>
     </row>
     <row r="40">
@@ -12102,7 +12689,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -12112,23 +12699,23 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>запас на конец месяца 261.083 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-02</t>
+          <t>пик запаса внутри месяца 185.587 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-11 (поставка одной партией в начале месяца; запас на начало 162.387 т, нетто-поступление 23.199 т, выдача 16.667 т)</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="G40" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I40" t="n">
-        <v>261.0825378333333</v>
+        <v>185.5865422333334</v>
       </c>
       <c r="J40" t="n">
         <v>120</v>
       </c>
       <c r="K40" t="n">
-        <v>141.0825378333333</v>
+        <v>65.5865422333334</v>
       </c>
     </row>
     <row r="41">
@@ -12154,23 +12741,23 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>запас на конец месяца 267.583 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-03</t>
+          <t>запас на конец месяца 175.452 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-12</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="G41" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I41" t="n">
-        <v>267.5825426</v>
+        <v>175.4523875000001</v>
       </c>
       <c r="J41" t="n">
         <v>120</v>
       </c>
       <c r="K41" t="n">
-        <v>147.5825426</v>
+        <v>55.4523875000001</v>
       </c>
     </row>
     <row r="42">
@@ -12186,7 +12773,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -12196,23 +12783,23 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>запас на конец месяца 274.083 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-04</t>
+          <t>пик запаса внутри месяца 192.119 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-12 (поставка одной партией в начале месяца; запас на начало 168.920 т, нетто-поступление 23.199 т, выдача 16.667 т)</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="G42" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I42" t="n">
-        <v>274.0825473666667</v>
+        <v>192.1190541666668</v>
       </c>
       <c r="J42" t="n">
         <v>120</v>
       </c>
       <c r="K42" t="n">
-        <v>154.0825473666667</v>
+        <v>72.11905416666676</v>
       </c>
     </row>
     <row r="43">
@@ -12238,23 +12825,23 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>запас на конец месяца 280.583 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-05</t>
+          <t>запас на конец месяца 181.505 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-01</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>280.5825521333334</v>
+        <v>181.5048992333334</v>
       </c>
       <c r="J43" t="n">
         <v>120</v>
       </c>
       <c r="K43" t="n">
-        <v>160.5825521333334</v>
+        <v>61.50489923333342</v>
       </c>
     </row>
     <row r="44">
@@ -12270,7 +12857,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -12280,23 +12867,23 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>запас на конец месяца 287.083 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-06</t>
+          <t>пик запаса внутри месяца 202.838 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-01 (поставка одной партией в начале месяца; запас на начало 175.452 т, нетто-поступление 27.386 т, выдача 21.333 т)</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G44" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>287.0825569</v>
+        <v>202.8382325666668</v>
       </c>
       <c r="J44" t="n">
         <v>120</v>
       </c>
       <c r="K44" t="n">
-        <v>167.0825569</v>
+        <v>82.83823256666676</v>
       </c>
     </row>
     <row r="45">
@@ -12322,23 +12909,23 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>запас на конец месяца 293.583 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-07</t>
+          <t>запас на конец месяца 187.557 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-02</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G45" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I45" t="n">
-        <v>293.5825616666667</v>
+        <v>187.5574109666667</v>
       </c>
       <c r="J45" t="n">
         <v>120</v>
       </c>
       <c r="K45" t="n">
-        <v>173.5825616666667</v>
+        <v>67.55741096666674</v>
       </c>
     </row>
     <row r="46">
@@ -12354,7 +12941,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -12364,23 +12951,23 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>запас на конец месяца 300.083 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-08</t>
+          <t>пик запаса внутри месяца 208.891 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-02 (поставка одной партией в начале месяца; запас на начало 181.505 т, нетто-поступление 27.386 т, выдача 21.333 т)</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G46" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I46" t="n">
-        <v>300.0825664333334</v>
+        <v>208.8907443000001</v>
       </c>
       <c r="J46" t="n">
         <v>120</v>
       </c>
       <c r="K46" t="n">
-        <v>180.0825664333334</v>
+        <v>88.89074430000008</v>
       </c>
     </row>
     <row r="47">
@@ -12406,23 +12993,23 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>запас на конец месяца 306.583 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-09</t>
+          <t>запас на конец месяца 193.610 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-03</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G47" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>306.5825712000001</v>
+        <v>193.6099227000001</v>
       </c>
       <c r="J47" t="n">
         <v>120</v>
       </c>
       <c r="K47" t="n">
-        <v>186.5825712000001</v>
+        <v>73.60992270000006</v>
       </c>
     </row>
     <row r="48">
@@ -12438,7 +13025,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -12448,23 +13035,23 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>запас на конец месяца 313.083 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-10</t>
+          <t>пик запаса внутри месяца 214.943 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-03 (поставка одной партией в начале месяца; запас на начало 187.557 т, нетто-поступление 27.386 т, выдача 21.333 т)</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G48" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>313.0825759666668</v>
+        <v>214.9432560333334</v>
       </c>
       <c r="J48" t="n">
         <v>120</v>
       </c>
       <c r="K48" t="n">
-        <v>193.0825759666668</v>
+        <v>94.9432560333334</v>
       </c>
     </row>
     <row r="49">
@@ -12490,23 +13077,23 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>запас на конец месяца 319.583 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-11</t>
+          <t>запас на конец месяца 199.662 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-04</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G49" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I49" t="n">
-        <v>319.5825807333334</v>
+        <v>199.6624344333334</v>
       </c>
       <c r="J49" t="n">
         <v>120</v>
       </c>
       <c r="K49" t="n">
-        <v>199.5825807333334</v>
+        <v>79.66243443333337</v>
       </c>
     </row>
     <row r="50">
@@ -12522,7 +13109,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -12532,23 +13119,1703 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>запас на конец месяца 326.083 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-12</t>
+          <t>пик запаса внутри месяца 220.996 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-04 (поставка одной партией в начале месяца; запас на начало 193.610 т, нетто-поступление 27.386 т, выдача 21.333 т)</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G50" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I50" t="n">
-        <v>326.0825855000001</v>
+        <v>220.9957677666667</v>
       </c>
       <c r="J50" t="n">
         <v>120</v>
       </c>
       <c r="K50" t="n">
+        <v>100.9957677666667</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 205.715 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-05</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>2039</v>
+      </c>
+      <c r="G51" t="n">
+        <v>5</v>
+      </c>
+      <c r="I51" t="n">
+        <v>205.7149461666667</v>
+      </c>
+      <c r="J51" t="n">
+        <v>120</v>
+      </c>
+      <c r="K51" t="n">
+        <v>85.71494616666669</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 227.048 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-05 (поставка одной партией в начале месяца; запас на начало 199.662 т, нетто-поступление 27.386 т, выдача 21.333 т)</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>2039</v>
+      </c>
+      <c r="G52" t="n">
+        <v>5</v>
+      </c>
+      <c r="I52" t="n">
+        <v>227.0482795</v>
+      </c>
+      <c r="J52" t="n">
+        <v>120</v>
+      </c>
+      <c r="K52" t="n">
+        <v>107.0482795</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 211.767 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-06</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>2039</v>
+      </c>
+      <c r="G53" t="n">
+        <v>6</v>
+      </c>
+      <c r="I53" t="n">
+        <v>211.7674579</v>
+      </c>
+      <c r="J53" t="n">
+        <v>120</v>
+      </c>
+      <c r="K53" t="n">
+        <v>91.76745790000001</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 233.101 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-06 (поставка одной партией в начале месяца; запас на начало 205.715 т, нетто-поступление 27.386 т, выдача 21.333 т)</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>2039</v>
+      </c>
+      <c r="G54" t="n">
+        <v>6</v>
+      </c>
+      <c r="I54" t="n">
+        <v>233.1007912333334</v>
+      </c>
+      <c r="J54" t="n">
+        <v>120</v>
+      </c>
+      <c r="K54" t="n">
+        <v>113.1007912333334</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 217.820 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-07</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>2039</v>
+      </c>
+      <c r="G55" t="n">
+        <v>7</v>
+      </c>
+      <c r="I55" t="n">
+        <v>217.8199696333333</v>
+      </c>
+      <c r="J55" t="n">
+        <v>120</v>
+      </c>
+      <c r="K55" t="n">
+        <v>97.81996963333333</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 239.153 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-07 (поставка одной партией в начале месяца; запас на начало 211.767 т, нетто-поступление 27.386 т, выдача 21.333 т)</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>2039</v>
+      </c>
+      <c r="G56" t="n">
+        <v>7</v>
+      </c>
+      <c r="I56" t="n">
+        <v>239.1533029666667</v>
+      </c>
+      <c r="J56" t="n">
+        <v>120</v>
+      </c>
+      <c r="K56" t="n">
+        <v>119.1533029666667</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 223.872 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-08</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>2039</v>
+      </c>
+      <c r="G57" t="n">
+        <v>8</v>
+      </c>
+      <c r="I57" t="n">
+        <v>223.8724813666666</v>
+      </c>
+      <c r="J57" t="n">
+        <v>120</v>
+      </c>
+      <c r="K57" t="n">
+        <v>103.8724813666666</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 245.206 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-08 (поставка одной партией в начале месяца; запас на начало 217.820 т, нетто-поступление 27.386 т, выдача 21.333 т)</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>2039</v>
+      </c>
+      <c r="G58" t="n">
+        <v>8</v>
+      </c>
+      <c r="I58" t="n">
+        <v>245.2058147</v>
+      </c>
+      <c r="J58" t="n">
+        <v>120</v>
+      </c>
+      <c r="K58" t="n">
+        <v>125.2058147</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 229.925 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-09</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>2039</v>
+      </c>
+      <c r="G59" t="n">
+        <v>9</v>
+      </c>
+      <c r="I59" t="n">
+        <v>229.9249931</v>
+      </c>
+      <c r="J59" t="n">
+        <v>120</v>
+      </c>
+      <c r="K59" t="n">
+        <v>109.9249931</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 251.258 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-09 (поставка одной партией в начале месяца; запас на начало 223.872 т, нетто-поступление 27.386 т, выдача 21.333 т)</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>2039</v>
+      </c>
+      <c r="G60" t="n">
+        <v>9</v>
+      </c>
+      <c r="I60" t="n">
+        <v>251.2583264333333</v>
+      </c>
+      <c r="J60" t="n">
+        <v>120</v>
+      </c>
+      <c r="K60" t="n">
+        <v>131.2583264333333</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 235.978 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-10</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>2039</v>
+      </c>
+      <c r="G61" t="n">
+        <v>10</v>
+      </c>
+      <c r="I61" t="n">
+        <v>235.9775048333333</v>
+      </c>
+      <c r="J61" t="n">
+        <v>120</v>
+      </c>
+      <c r="K61" t="n">
+        <v>115.9775048333333</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 257.311 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-10 (поставка одной партией в начале месяца; запас на начало 229.925 т, нетто-поступление 27.386 т, выдача 21.333 т)</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>2039</v>
+      </c>
+      <c r="G62" t="n">
+        <v>10</v>
+      </c>
+      <c r="I62" t="n">
+        <v>257.3108381666667</v>
+      </c>
+      <c r="J62" t="n">
+        <v>120</v>
+      </c>
+      <c r="K62" t="n">
+        <v>137.3108381666667</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 242.030 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-11</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>2039</v>
+      </c>
+      <c r="G63" t="n">
+        <v>11</v>
+      </c>
+      <c r="I63" t="n">
+        <v>242.0300165666667</v>
+      </c>
+      <c r="J63" t="n">
+        <v>120</v>
+      </c>
+      <c r="K63" t="n">
+        <v>122.0300165666667</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 263.363 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-11 (поставка одной партией в начале месяца; запас на начало 235.978 т, нетто-поступление 27.386 т, выдача 21.333 т)</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>2039</v>
+      </c>
+      <c r="G64" t="n">
+        <v>11</v>
+      </c>
+      <c r="I64" t="n">
+        <v>263.3633499</v>
+      </c>
+      <c r="J64" t="n">
+        <v>120</v>
+      </c>
+      <c r="K64" t="n">
+        <v>143.3633499</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 248.083 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-12</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>2039</v>
+      </c>
+      <c r="G65" t="n">
+        <v>12</v>
+      </c>
+      <c r="I65" t="n">
+        <v>248.0825283</v>
+      </c>
+      <c r="J65" t="n">
+        <v>120</v>
+      </c>
+      <c r="K65" t="n">
+        <v>128.0825283</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 269.416 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-12 (поставка одной партией в начале месяца; запас на начало 242.030 т, нетто-поступление 27.386 т, выдача 21.333 т)</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>2039</v>
+      </c>
+      <c r="G66" t="n">
+        <v>12</v>
+      </c>
+      <c r="I66" t="n">
+        <v>269.4158616333333</v>
+      </c>
+      <c r="J66" t="n">
+        <v>120</v>
+      </c>
+      <c r="K66" t="n">
+        <v>149.4158616333333</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 254.583 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-01</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" t="n">
+        <v>254.5825330666667</v>
+      </c>
+      <c r="J67" t="n">
+        <v>120</v>
+      </c>
+      <c r="K67" t="n">
+        <v>134.5825330666667</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 280.583 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-01 (поставка одной партией в начале месяца; запас на начало 248.083 т, нетто-поступление 32.500 т, выдача 26.000 т)</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" t="n">
+        <v>280.5825330666667</v>
+      </c>
+      <c r="J68" t="n">
+        <v>120</v>
+      </c>
+      <c r="K68" t="n">
+        <v>160.5825330666667</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 261.083 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-02</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2</v>
+      </c>
+      <c r="I69" t="n">
+        <v>261.0825378333333</v>
+      </c>
+      <c r="J69" t="n">
+        <v>120</v>
+      </c>
+      <c r="K69" t="n">
+        <v>141.0825378333333</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 287.083 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-02 (поставка одной партией в начале месяца; запас на начало 254.583 т, нетто-поступление 32.500 т, выдача 26.000 т)</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G70" t="n">
+        <v>2</v>
+      </c>
+      <c r="I70" t="n">
+        <v>287.0825378333333</v>
+      </c>
+      <c r="J70" t="n">
+        <v>120</v>
+      </c>
+      <c r="K70" t="n">
+        <v>167.0825378333333</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 267.583 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-03</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G71" t="n">
+        <v>3</v>
+      </c>
+      <c r="I71" t="n">
+        <v>267.5825426</v>
+      </c>
+      <c r="J71" t="n">
+        <v>120</v>
+      </c>
+      <c r="K71" t="n">
+        <v>147.5825426</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 293.583 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-03 (поставка одной партией в начале месяца; запас на начало 261.083 т, нетто-поступление 32.500 т, выдача 26.000 т)</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G72" t="n">
+        <v>3</v>
+      </c>
+      <c r="I72" t="n">
+        <v>293.5825426</v>
+      </c>
+      <c r="J72" t="n">
+        <v>120</v>
+      </c>
+      <c r="K72" t="n">
+        <v>173.5825426</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 274.083 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-04</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G73" t="n">
+        <v>4</v>
+      </c>
+      <c r="I73" t="n">
+        <v>274.0825473666667</v>
+      </c>
+      <c r="J73" t="n">
+        <v>120</v>
+      </c>
+      <c r="K73" t="n">
+        <v>154.0825473666667</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 300.083 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-04 (поставка одной партией в начале месяца; запас на начало 267.583 т, нетто-поступление 32.500 т, выдача 26.000 т)</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G74" t="n">
+        <v>4</v>
+      </c>
+      <c r="I74" t="n">
+        <v>300.0825473666667</v>
+      </c>
+      <c r="J74" t="n">
+        <v>120</v>
+      </c>
+      <c r="K74" t="n">
+        <v>180.0825473666667</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 280.583 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-05</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5</v>
+      </c>
+      <c r="I75" t="n">
+        <v>280.5825521333334</v>
+      </c>
+      <c r="J75" t="n">
+        <v>120</v>
+      </c>
+      <c r="K75" t="n">
+        <v>160.5825521333334</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 306.583 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-05 (поставка одной партией в начале месяца; запас на начало 274.083 т, нетто-поступление 32.500 т, выдача 26.000 т)</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G76" t="n">
+        <v>5</v>
+      </c>
+      <c r="I76" t="n">
+        <v>306.5825521333334</v>
+      </c>
+      <c r="J76" t="n">
+        <v>120</v>
+      </c>
+      <c r="K76" t="n">
+        <v>186.5825521333334</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 287.083 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-06</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G77" t="n">
+        <v>6</v>
+      </c>
+      <c r="I77" t="n">
+        <v>287.0825569</v>
+      </c>
+      <c r="J77" t="n">
+        <v>120</v>
+      </c>
+      <c r="K77" t="n">
+        <v>167.0825569</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 313.083 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-06 (поставка одной партией в начале месяца; запас на начало 280.583 т, нетто-поступление 32.500 т, выдача 26.000 т)</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G78" t="n">
+        <v>6</v>
+      </c>
+      <c r="I78" t="n">
+        <v>313.0825569</v>
+      </c>
+      <c r="J78" t="n">
+        <v>120</v>
+      </c>
+      <c r="K78" t="n">
+        <v>193.0825569</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 293.583 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-07</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G79" t="n">
+        <v>7</v>
+      </c>
+      <c r="I79" t="n">
+        <v>293.5825616666667</v>
+      </c>
+      <c r="J79" t="n">
+        <v>120</v>
+      </c>
+      <c r="K79" t="n">
+        <v>173.5825616666667</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 319.583 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-07 (поставка одной партией в начале месяца; запас на начало 287.083 т, нетто-поступление 32.500 т, выдача 26.000 т)</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G80" t="n">
+        <v>7</v>
+      </c>
+      <c r="I80" t="n">
+        <v>319.5825616666667</v>
+      </c>
+      <c r="J80" t="n">
+        <v>120</v>
+      </c>
+      <c r="K80" t="n">
+        <v>199.5825616666667</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 300.083 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-08</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G81" t="n">
+        <v>8</v>
+      </c>
+      <c r="I81" t="n">
+        <v>300.0825664333334</v>
+      </c>
+      <c r="J81" t="n">
+        <v>120</v>
+      </c>
+      <c r="K81" t="n">
+        <v>180.0825664333334</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 326.083 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-08 (поставка одной партией в начале месяца; запас на начало 293.583 т, нетто-поступление 32.500 т, выдача 26.000 т)</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G82" t="n">
+        <v>8</v>
+      </c>
+      <c r="I82" t="n">
+        <v>326.0825664333334</v>
+      </c>
+      <c r="J82" t="n">
+        <v>120</v>
+      </c>
+      <c r="K82" t="n">
+        <v>206.0825664333334</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 306.583 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-09</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G83" t="n">
+        <v>9</v>
+      </c>
+      <c r="I83" t="n">
+        <v>306.5825712000001</v>
+      </c>
+      <c r="J83" t="n">
+        <v>120</v>
+      </c>
+      <c r="K83" t="n">
+        <v>186.5825712000001</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 332.583 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-09 (поставка одной партией в начале месяца; запас на начало 300.083 т, нетто-поступление 32.500 т, выдача 26.000 т)</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G84" t="n">
+        <v>9</v>
+      </c>
+      <c r="I84" t="n">
+        <v>332.5825712000001</v>
+      </c>
+      <c r="J84" t="n">
+        <v>120</v>
+      </c>
+      <c r="K84" t="n">
+        <v>212.5825712000001</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 313.083 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-10</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G85" t="n">
+        <v>10</v>
+      </c>
+      <c r="I85" t="n">
+        <v>313.0825759666668</v>
+      </c>
+      <c r="J85" t="n">
+        <v>120</v>
+      </c>
+      <c r="K85" t="n">
+        <v>193.0825759666668</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 339.083 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-10 (поставка одной партией в начале месяца; запас на начало 306.583 т, нетто-поступление 32.500 т, выдача 26.000 т)</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G86" t="n">
+        <v>10</v>
+      </c>
+      <c r="I86" t="n">
+        <v>339.0825759666668</v>
+      </c>
+      <c r="J86" t="n">
+        <v>120</v>
+      </c>
+      <c r="K86" t="n">
+        <v>219.0825759666668</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 319.583 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-11</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G87" t="n">
+        <v>11</v>
+      </c>
+      <c r="I87" t="n">
+        <v>319.5825807333334</v>
+      </c>
+      <c r="J87" t="n">
+        <v>120</v>
+      </c>
+      <c r="K87" t="n">
+        <v>199.5825807333334</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 345.583 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-11 (поставка одной партией в начале месяца; запас на начало 313.083 т, нетто-поступление 32.500 т, выдача 26.000 т)</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G88" t="n">
+        <v>11</v>
+      </c>
+      <c r="I88" t="n">
+        <v>345.5825807333334</v>
+      </c>
+      <c r="J88" t="n">
+        <v>120</v>
+      </c>
+      <c r="K88" t="n">
+        <v>225.5825807333334</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 326.083 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-12</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G89" t="n">
+        <v>12</v>
+      </c>
+      <c r="I89" t="n">
+        <v>326.0825855000001</v>
+      </c>
+      <c r="J89" t="n">
+        <v>120</v>
+      </c>
+      <c r="K89" t="n">
         <v>206.0825855000001</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 352.083 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-12 (поставка одной партией в начале месяца; запас на начало 319.583 т, нетто-поступление 32.500 т, выдача 26.000 т)</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G90" t="n">
+        <v>12</v>
+      </c>
+      <c r="I90" t="n">
+        <v>352.0825855000001</v>
+      </c>
+      <c r="J90" t="n">
+        <v>120</v>
+      </c>
+      <c r="K90" t="n">
+        <v>232.0825855000001</v>
       </c>
     </row>
   </sheetData>
@@ -12562,7 +14829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14253,7 +16520,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -14261,14 +16528,14 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>109.876</v>
+        <v>43.92710566666667</v>
       </c>
       <c r="G36" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -14285,7 +16552,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2035-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -14302,7 +16569,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -14310,14 +16577,14 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>109.876</v>
       </c>
       <c r="G37" t="n">
-        <v>109.876</v>
+        <v>190</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -14351,7 +16618,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -14359,18 +16626,19 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>all_deliveries_ordered_within_lead_time</t>
+          <t>ordered_A_t</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>109.876</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38">
-        <f>=</f>
-        <v/>
+        <v>109.876</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="I38" t="b">
         <v>1</v>
@@ -14380,7 +16648,11 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -14395,7 +16667,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SOURCE_NOT_AVAILABLE</t>
+          <t>LEAD_TIME_VIOLATED</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -14403,7 +16675,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>all_orders_from_available_sources</t>
+          <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -14439,41 +16711,36 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
+          <t>all_orders_from_available_sources</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>71.42490800000002</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>70</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H40">
+        <f>=</f>
+        <v/>
       </c>
       <c r="I40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>2036-12, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -14488,7 +16755,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -14496,14 +16763,14 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>153.052</v>
+        <v>71.42490800000002</v>
       </c>
       <c r="G41" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -14511,7 +16778,7 @@
         </is>
       </c>
       <c r="I41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -14520,7 +16787,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14537,7 +16804,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -14545,14 +16812,14 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>153.0518</v>
+        <v>80.75824133333334</v>
       </c>
       <c r="G42" t="n">
-        <v>153.052</v>
+        <v>70</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -14560,7 +16827,7 @@
         </is>
       </c>
       <c r="I42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -14569,7 +16836,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -14586,7 +16853,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -14594,170 +16861,170 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="G43" t="n">
+        <v>190</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I43" t="b">
+        <v>1</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>153.0518</v>
+      </c>
+      <c r="G44" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I44" t="b">
+        <v>1</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43">
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45">
         <f>=</f>
         <v/>
       </c>
-      <c r="I43" t="b">
-        <v>1</v>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="I45" t="b">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D46" t="n">
         <v>2036</v>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44">
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46">
         <f>=</f>
         <v/>
       </c>
-      <c r="I44" t="b">
-        <v>1</v>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>92.44727349999999</v>
-      </c>
-      <c r="G45" t="n">
-        <v>70</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I45" t="b">
-        <v>0</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>2037-06, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>190</v>
-      </c>
-      <c r="G46" t="n">
-        <v>190</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I46" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -14772,7 +17039,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -14780,14 +17047,14 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>190</v>
+        <v>92.44727349999999</v>
       </c>
       <c r="G47" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -14795,7 +17062,7 @@
         </is>
       </c>
       <c r="I47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -14804,7 +17071,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2037-06, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14821,7 +17088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -14829,14 +17096,14 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>reserved_B_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>13.189</v>
+        <v>105.1139401666667</v>
       </c>
       <c r="G48" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -14844,7 +17111,7 @@
         </is>
       </c>
       <c r="I48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -14853,7 +17120,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>2037-06, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -14870,7 +17137,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -14878,14 +17145,14 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ordered_B_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>13.1882</v>
+        <v>190</v>
       </c>
       <c r="G49" t="n">
-        <v>13.189</v>
+        <v>190</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -14902,7 +17169,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -14919,7 +17186,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -14927,219 +17194,219 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>190</v>
+      </c>
+      <c r="G50" t="n">
+        <v>190</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I50" t="b">
+        <v>1</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>13.189</v>
+      </c>
+      <c r="G51" t="n">
+        <v>110</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I51" t="b">
+        <v>1</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>13.1882</v>
+      </c>
+      <c r="G52" t="n">
+        <v>13.189</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I52" t="b">
+        <v>1</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50">
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53">
         <f>=</f>
         <v/>
       </c>
-      <c r="I50" t="b">
-        <v>1</v>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
+      <c r="K53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D54" t="n">
         <v>2037</v>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51">
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54">
         <f>=</f>
         <v/>
       </c>
-      <c r="I51" t="b">
-        <v>1</v>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>175.4523875000001</v>
-      </c>
-      <c r="G52" t="n">
-        <v>120</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I52" t="b">
-        <v>0</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>2038-12, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>161.772</v>
-      </c>
-      <c r="G53" t="n">
-        <v>190</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I53" t="b">
-        <v>1</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>161.7714</v>
-      </c>
-      <c r="G54" t="n">
-        <v>161.772</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I54" t="b">
-        <v>1</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -15154,7 +17421,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -15162,11 +17429,11 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>120</v>
+        <v>175.4523875000001</v>
       </c>
       <c r="G55" t="n">
         <v>120</v>
@@ -15177,7 +17444,7 @@
         </is>
       </c>
       <c r="I55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -15186,7 +17453,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2038-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -15203,7 +17470,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -15211,14 +17478,14 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>100</v>
+        <v>192.1190541666668</v>
       </c>
       <c r="G56" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -15226,7 +17493,7 @@
         </is>
       </c>
       <c r="I56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -15235,7 +17502,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2038-12, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -15252,7 +17519,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -15260,268 +17527,268 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>161.772</v>
+      </c>
+      <c r="G57" t="n">
+        <v>190</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>161.7714</v>
+      </c>
+      <c r="G58" t="n">
+        <v>161.772</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I58" t="b">
+        <v>1</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>120</v>
+      </c>
+      <c r="G59" t="n">
+        <v>120</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I59" t="b">
+        <v>1</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>100</v>
+      </c>
+      <c r="G60" t="n">
+        <v>100</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I60" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F57" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" t="n">
-        <v>1</v>
-      </c>
-      <c r="H57">
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61">
         <f>=</f>
         <v/>
       </c>
-      <c r="I57" t="b">
-        <v>1</v>
-      </c>
-      <c r="J57" t="inlineStr">
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
+      <c r="K61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D62" t="n">
         <v>2038</v>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F58" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" t="n">
-        <v>1</v>
-      </c>
-      <c r="H58">
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62">
         <f>=</f>
         <v/>
       </c>
-      <c r="I58" t="b">
-        <v>1</v>
-      </c>
-      <c r="J58" t="inlineStr">
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>248.0825283</v>
-      </c>
-      <c r="G59" t="n">
-        <v>120</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I59" t="b">
-        <v>0</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>2039-12, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>190</v>
-      </c>
-      <c r="G60" t="n">
-        <v>190</v>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I60" t="b">
-        <v>1</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>190</v>
-      </c>
-      <c r="G61" t="n">
-        <v>190</v>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I61" t="b">
-        <v>1</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>reserved_B_t_per_year</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>22.622</v>
-      </c>
-      <c r="G62" t="n">
-        <v>110</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I62" t="b">
-        <v>1</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
+      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -15536,7 +17803,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -15544,14 +17811,14 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ordered_B_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>22.6216</v>
+        <v>248.0825283</v>
       </c>
       <c r="G63" t="n">
-        <v>22.622</v>
+        <v>120</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -15559,7 +17826,7 @@
         </is>
       </c>
       <c r="I63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -15568,7 +17835,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>2039-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -15585,7 +17852,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -15593,11 +17860,11 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>120</v>
+        <v>269.4158616333333</v>
       </c>
       <c r="G64" t="n">
         <v>120</v>
@@ -15608,7 +17875,7 @@
         </is>
       </c>
       <c r="I64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -15617,7 +17884,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2039-12, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -15634,7 +17901,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -15642,14 +17909,14 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="G65" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -15666,7 +17933,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -15683,7 +17950,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -15691,317 +17958,317 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>190</v>
+      </c>
+      <c r="G66" t="n">
+        <v>190</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I66" t="b">
+        <v>1</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>22.622</v>
+      </c>
+      <c r="G67" t="n">
+        <v>110</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I67" t="b">
+        <v>1</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>22.6216</v>
+      </c>
+      <c r="G68" t="n">
+        <v>22.622</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I68" t="b">
+        <v>1</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>120</v>
+      </c>
+      <c r="G69" t="n">
+        <v>120</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I69" t="b">
+        <v>1</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>120</v>
+      </c>
+      <c r="G70" t="n">
+        <v>120</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I70" t="b">
+        <v>1</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F66" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" t="n">
-        <v>1</v>
-      </c>
-      <c r="H66">
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71">
         <f>=</f>
         <v/>
       </c>
-      <c r="I66" t="b">
-        <v>1</v>
-      </c>
-      <c r="J66" t="inlineStr">
+      <c r="I71" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
+      <c r="K71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D72" t="n">
         <v>2039</v>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" t="n">
-        <v>1</v>
-      </c>
-      <c r="H67">
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72">
         <f>=</f>
         <v/>
       </c>
-      <c r="I67" t="b">
-        <v>1</v>
-      </c>
-      <c r="J67" t="inlineStr">
+      <c r="I72" t="b">
+        <v>1</v>
+      </c>
+      <c r="J72" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>326.0825855000001</v>
-      </c>
-      <c r="G68" t="n">
-        <v>120</v>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I68" t="b">
-        <v>0</v>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>2040-12, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>190</v>
-      </c>
-      <c r="G69" t="n">
-        <v>190</v>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I69" t="b">
-        <v>1</v>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>190</v>
-      </c>
-      <c r="G70" t="n">
-        <v>190</v>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I70" t="b">
-        <v>1</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>reserved_B_t_per_year</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>84.73699999999999</v>
-      </c>
-      <c r="G71" t="n">
-        <v>110</v>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I71" t="b">
-        <v>1</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>ordered_B_t</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>84.73690000000001</v>
-      </c>
-      <c r="G72" t="n">
-        <v>84.73699999999999</v>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I72" t="b">
-        <v>1</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
+      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -16016,7 +18283,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -16024,11 +18291,11 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>120</v>
+        <v>326.0825855000001</v>
       </c>
       <c r="G73" t="n">
         <v>120</v>
@@ -16039,7 +18306,7 @@
         </is>
       </c>
       <c r="I73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -16048,7 +18315,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2040-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -16065,7 +18332,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -16073,11 +18340,11 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>120</v>
+        <v>352.0825855000001</v>
       </c>
       <c r="G74" t="n">
         <v>120</v>
@@ -16088,7 +18355,7 @@
         </is>
       </c>
       <c r="I74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -16097,7 +18364,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2040-12, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -16114,7 +18381,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -16122,72 +18389,366 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>190</v>
+      </c>
+      <c r="G75" t="n">
+        <v>190</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I75" t="b">
+        <v>1</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>190</v>
+      </c>
+      <c r="G76" t="n">
+        <v>190</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I76" t="b">
+        <v>1</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>84.73699999999999</v>
+      </c>
+      <c r="G77" t="n">
+        <v>110</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I77" t="b">
+        <v>1</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>84.73690000000001</v>
+      </c>
+      <c r="G78" t="n">
+        <v>84.73699999999999</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I78" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>120</v>
+      </c>
+      <c r="G79" t="n">
+        <v>120</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I79" t="b">
+        <v>1</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>120</v>
+      </c>
+      <c r="G80" t="n">
+        <v>120</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I80" t="b">
+        <v>1</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F75" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75">
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81">
         <f>=</f>
         <v/>
       </c>
-      <c r="I75" t="b">
-        <v>1</v>
-      </c>
-      <c r="J75" t="inlineStr">
+      <c r="I81" t="b">
+        <v>1</v>
+      </c>
+      <c r="J81" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
+      <c r="K81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D82" t="n">
         <v>2040</v>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" t="n">
-        <v>1</v>
-      </c>
-      <c r="H76">
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82">
         <f>=</f>
         <v/>
       </c>
-      <c r="I76" t="b">
-        <v>1</v>
-      </c>
-      <c r="J76" t="inlineStr">
+      <c r="I82" t="b">
+        <v>1</v>
+      </c>
+      <c r="J82" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24806,7 +27367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24848,7 +27409,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11107.138816178</v>
+        <v>11107.508681948</v>
       </c>
     </row>
     <row r="3">
@@ -24868,7 +27429,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8979.548667767933</v>
+        <v>8979.918533537933</v>
       </c>
     </row>
     <row r="4">
@@ -25008,7 +27569,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9.988434187210432</v>
+        <v>9.98876680031295</v>
       </c>
     </row>
     <row r="11">
@@ -25028,7 +27589,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8.075133694035911</v>
+        <v>8.075466307138429</v>
       </c>
     </row>
     <row r="12">
@@ -25188,7 +27749,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>582.6072561780001</v>
+        <v>582.9771219480001</v>
       </c>
     </row>
     <row r="20">
@@ -25304,11 +27865,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>prep_holding_mln</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>40</v>
+        <v>0.36986577</v>
       </c>
     </row>
     <row r="26">
@@ -25324,11 +27885,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>prep_holding_months</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -25344,11 +27905,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>9</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28">
@@ -25364,10 +27925,10 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D28" t="b">
+          <t>guideline_violations</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -25384,11 +27945,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>checks_total</t>
+          <t>warnings</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -25404,11 +27965,51 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>70</v>
+      <c r="D32" t="n">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
